--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,61 +749,64 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E8" s="3">
         <v>158500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>160100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>166300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>164900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>144200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>137000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>78100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>66300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>84100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>83100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -811,56 +814,59 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E9" s="3">
         <v>79300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>80700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>79300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>80800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>83300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>78700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>72500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>72800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,56 +879,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E10" s="3">
         <v>79200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>79400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>87100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>84200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>77400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>81700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>64200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>52200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>51600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>52300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +971,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -968,47 +981,47 @@
         <v>24900</v>
       </c>
       <c r="E12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F12" s="3">
         <v>25900</v>
-      </c>
-      <c r="F12" s="3">
-        <v>24900</v>
       </c>
       <c r="G12" s="3">
         <v>24900</v>
       </c>
       <c r="H12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="I12" s="3">
         <v>25600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14600</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,61 +1099,64 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>717700</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>410400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>388700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>520400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>33200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1145,8 +1164,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,52 +1176,52 @@
         <v>20000</v>
       </c>
       <c r="E15" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F15" s="3">
         <v>20100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>19500</v>
       </c>
       <c r="K15" s="3">
         <v>19500</v>
       </c>
       <c r="L15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="M15" s="3">
         <v>3500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1207,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,58 +1253,59 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>888900</v>
+      </c>
+      <c r="E17" s="3">
         <v>184400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>582800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>555100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>171100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>696400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>174000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>191400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>91100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>121900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>83900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>79300</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1290,56 +1316,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-731400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-422700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-388800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-535700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,56 +1408,57 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-35000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>64300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-140400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>42800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,56 +1471,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-691800</v>
+      </c>
+      <c r="E21" s="3">
         <v>13200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-373800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-370400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>50100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-469100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>92200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-147600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1536,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1509,16 +1548,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1530,14 +1569,14 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1586,8 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1562,58 +1601,61 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-745400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-427200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-423900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-523200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-75100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-168000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15600</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1624,61 +1666,64 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-66300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-120400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-113700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-26700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-31400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8200</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1686,8 +1731,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,58 +1796,61 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-740000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-360900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-303500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-409600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>67700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-169400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>33300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23800</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1810,58 +1861,61 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-667600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-325400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-273500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-368700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-59200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-142300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,56 +2186,59 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>14800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>35000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-64300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>140400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-42800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>16300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,58 +2251,61 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-667600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-325400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-273500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-368700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>56200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-59200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-142300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,58 +2381,61 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-667600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-325400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-273500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-368700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>56200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-59200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-142300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2368,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,44 +2568,45 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110300</v>
+      </c>
+      <c r="E41" s="3">
         <v>111800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>93000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>85700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>98100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>129200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>155500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>56500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>473100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>220700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2631,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,44 +2696,47 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E43" s="3">
         <v>127500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>132100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>179400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>154100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>160100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>123300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>155300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>104600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>67600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>60600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2660,8 +2752,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2669,8 +2761,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2731,44 +2826,47 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E45" s="3">
         <v>48300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>51200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>45300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,12 +2876,12 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,44 +2891,47 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E46" s="3">
         <v>287600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>287700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>304400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>274700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>300800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>303600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>356100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>205100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>570300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>305300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2840,12 +2941,12 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2956,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2872,8 +2976,8 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
-        <v>200</v>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
         <v>200</v>
@@ -2890,8 +2994,8 @@
       <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>200</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2917,44 +3021,47 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E48" s="3">
         <v>88200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>91800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>94100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>101800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>101700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>82300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2970,8 +3077,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2979,44 +3086,47 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2732600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3493000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3525600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3978900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4402000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4428800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5040500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4938300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4986600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3423000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3440800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3032,8 +3142,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3041,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,44 +3281,47 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E52" s="3">
         <v>27100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,8 +3337,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3227,8 +3346,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,44 +3411,47 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3140500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3895900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3931100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4400200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4792400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4852200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5466000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5405500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5289200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4070800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3823100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3336,12 +3461,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>1300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,44 +3528,45 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E57" s="3">
         <v>31200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>51600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,12 +3576,12 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,44 +3591,47 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E58" s="3">
         <v>11700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3514,8 +3647,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3523,44 +3656,47 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>255800</v>
+      </c>
+      <c r="E59" s="3">
         <v>263700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>261200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>287000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>281100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>334000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>357800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>313600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>189700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>408900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>121800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3570,12 +3706,12 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,44 +3721,47 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300400</v>
+      </c>
+      <c r="E60" s="3">
         <v>306600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>305800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>336200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>339800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>388800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>406500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>440400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>295600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>473600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>181400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3632,12 +3771,12 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,44 +3786,47 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1042100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1041300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1043000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1044700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1042500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1046500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1050000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>865500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>869600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>504800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>509000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3709,44 +3851,47 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>172200</v>
+      </c>
+      <c r="E62" s="3">
         <v>188300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>205600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>292400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>392400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>422200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>566700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>615400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>717100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>657600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>821200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,12 +3901,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,44 +4111,47 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1625200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1719900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1741800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1896300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2028400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2111100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2320200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2219700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2182500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1955700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1877400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,12 +4161,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>1300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,44 +4461,47 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1831500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-803700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-530200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-535000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-166300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-155000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-211200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-152000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-131500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,11 +4511,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,44 +4721,47 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1515300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2176000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2189300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2503900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2764000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2741200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3145800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3185800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3106700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2115100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1945700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4586,11 +4771,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4601,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,58 +4921,61 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-667600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-325400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-273500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-368700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>56200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-59200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-142300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,61 +5013,62 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E83" s="3">
         <v>53800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>53400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>54100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>53300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>51100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4878,8 +5076,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,58 +5401,61 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E89" s="3">
         <v>14800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>36500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>39300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29800</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,61 +5493,62 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>-3900</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5336,8 +5556,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,61 +5686,64 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-146400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-781500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-469200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-3900</v>
       </c>
       <c r="Q94" s="3">
         <v>-3900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>-3900</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5522,8 +5751,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,56 +6036,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>102300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>379700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>254000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>634100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,61 +6101,64 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -5918,58 +6166,61 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>103000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-412200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>251100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>149100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -5978,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,64 +753,67 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>158400</v>
+      </c>
+      <c r="E8" s="3">
         <v>157500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>158500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>160100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>166300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>164900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>144200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>137000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>78100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>84100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>83100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -817,59 +821,62 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E9" s="3">
         <v>78900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>79300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>79300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>83300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>78700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>72500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>39600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>38200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,59 +889,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E10" s="3">
         <v>78600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>79200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>87100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>84200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>81700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>52200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>51600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>52300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,59 +985,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>24900</v>
+        <v>25700</v>
       </c>
       <c r="E12" s="3">
         <v>24900</v>
       </c>
       <c r="F12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="G12" s="3">
         <v>25900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>24900</v>
       </c>
       <c r="H12" s="3">
         <v>24900</v>
       </c>
       <c r="I12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="J12" s="3">
         <v>25600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,64 +1119,67 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>717700</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>410400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>388700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>520400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>33200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1167,64 +1187,67 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20000</v>
+        <v>20100</v>
       </c>
       <c r="E15" s="3">
         <v>20000</v>
       </c>
       <c r="F15" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G15" s="3">
         <v>20100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>19500</v>
       </c>
       <c r="L15" s="3">
         <v>19500</v>
       </c>
       <c r="M15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="N15" s="3">
         <v>3500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8500</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,61 +1280,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E17" s="3">
         <v>888900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>184400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>582800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>555100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>171100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>696400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>174000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>191400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>91100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>121900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>83900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>76800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>79300</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,59 +1346,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-731400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-25900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-422700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-388800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-535700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-27400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,59 +1442,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-35000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>64300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-140400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>42800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-16300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,59 +1508,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-691800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-373800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-370400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>50100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-469100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>92200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-147600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,28 +1576,31 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1572,14 +1612,14 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,8 +1629,8 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-745400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-427200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-423900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-523200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-75100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-168000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15600</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,64 +1712,67 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-66300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-120400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-113700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-8500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-26700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-31400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-740000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-360900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-303500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-409600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>67700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-169400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23800</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-667600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-325400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-273500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-368700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>56200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-59200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-142300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23800</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,59 +2256,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E32" s="3">
         <v>14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>35000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-64300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>140400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-42800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>16300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-667600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-325400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-273500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-368700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>56200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-59200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-142300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23800</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-667600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-325400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-273500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-368700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>56200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-59200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-142300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23800</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,47 +2655,48 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E41" s="3">
         <v>110300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>85700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>98100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>129200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>155500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>56500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>473100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>220700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,47 +2789,50 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E43" s="3">
         <v>132000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>132100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>179400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>154100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>160100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>123300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>155300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>104600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>67600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,8 +2848,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2829,47 +2925,50 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E45" s="3">
         <v>45500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,12 +2978,12 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,47 +2993,50 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>339400</v>
+      </c>
+      <c r="E46" s="3">
         <v>287800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>287600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>287700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>304400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>274700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>300800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>303600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>356100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>205100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>570300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>305300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2944,12 +3046,12 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2979,8 +3084,8 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
-        <v>200</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>200</v>
@@ -2997,8 +3102,8 @@
       <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>200</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -3024,47 +3129,50 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E48" s="3">
         <v>91600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>91200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>101800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>101700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>82300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3188,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3089,47 +3197,50 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2684500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2732600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3493000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3525600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3978900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4402000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4428800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5040500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4938300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4986600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3423000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3440800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3256,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,47 +3401,50 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E52" s="3">
         <v>28600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3460,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,47 +3537,50 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3141700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3140500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3895900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3931100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4400200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4792400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4852200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5466000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5405500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5289200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4070800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3823100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3464,12 +3590,12 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>1300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,47 +3659,48 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E57" s="3">
         <v>32300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>58300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>51600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3579,12 +3710,12 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,47 +3725,50 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E58" s="3">
         <v>12200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>91400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3650,8 +3784,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3659,47 +3793,50 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E59" s="3">
         <v>255800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>263700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>261200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>287000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>281100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>334000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>357800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>313600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>189700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>408900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>121800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,12 +3846,12 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,47 +3861,50 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E60" s="3">
         <v>300400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>306600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>305800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>336200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>339800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>388800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>406500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>440400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>295600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>473600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>181400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3774,12 +3914,12 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,47 +3929,50 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1041200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1042100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1041300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1043000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1044700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1042500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1046500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1050000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>865500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>869600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>504800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>509000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3854,47 +3997,50 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>176300</v>
+      </c>
+      <c r="E62" s="3">
         <v>172200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>188300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>205600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>292400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>392400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>422200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>566700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>615400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>717100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>657600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>821200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,12 +4050,12 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,47 +4269,50 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1656900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1625200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1719900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1741800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1896300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2028400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2111100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2320200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2219700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2182500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1955700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1877400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4164,12 +4322,12 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>1300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,47 +4635,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1873700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1831500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-803700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-530200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-535000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-166300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-155000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-211200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-152000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-131500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,11 +4688,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,47 +4907,50 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1484700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1515300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2176000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2189300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2503900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2764000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2741200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3145800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3185800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3106700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2115100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1945700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4774,11 +4960,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-667600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-325400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-273500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-368700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>56200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-59200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-142300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23800</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,64 +5212,65 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E83" s="3">
         <v>53600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>53300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>50500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,61 +5618,64 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>36500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>39300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29800</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,64 +5714,65 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-3900</v>
       </c>
       <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>-3900</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,64 +5916,67 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-781500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-469200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-3900</v>
       </c>
       <c r="R94" s="3">
         <v>-3900</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>-3900</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,59 +6282,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>102300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>77700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>379700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>254000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>634100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>12300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,64 +6350,67 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6169,61 +6418,64 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>103000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-412200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>251100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>149100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,67 +757,70 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E8" s="3">
         <v>158400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>157500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>160100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>166300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>164900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>144200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>137000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>78100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>84100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>83100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -824,62 +828,65 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E9" s="3">
         <v>77900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>78900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>79300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>80700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>79300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>80800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>83300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>38200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,62 +899,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E10" s="3">
         <v>80500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>79400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>87100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>84200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>52200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>51600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,62 +999,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E12" s="3">
         <v>25700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>24900</v>
       </c>
       <c r="F12" s="3">
         <v>24900</v>
       </c>
       <c r="G12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="H12" s="3">
         <v>25900</v>
-      </c>
-      <c r="H12" s="3">
-        <v>24900</v>
       </c>
       <c r="I12" s="3">
         <v>24900</v>
       </c>
       <c r="J12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K12" s="3">
         <v>25600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,67 +1139,70 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>717700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>410400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>388700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>520400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>33200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1199,58 +1222,58 @@
         <v>20100</v>
       </c>
       <c r="E15" s="3">
-        <v>20000</v>
+        <v>20100</v>
       </c>
       <c r="F15" s="3">
         <v>20000</v>
       </c>
       <c r="G15" s="3">
+        <v>20000</v>
+      </c>
+      <c r="H15" s="3">
         <v>20100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>19500</v>
       </c>
       <c r="M15" s="3">
         <v>19500</v>
       </c>
       <c r="N15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8500</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,64 +1307,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E17" s="3">
         <v>172100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>888900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>184400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>582800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>555100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>696400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>174000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>191400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>91100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>93700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>121900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>83900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>76800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>79300</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1349,62 +1376,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-731400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-422700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-388800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-535700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-27400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,62 +1476,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-40300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-14800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>64300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-20500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-140400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>42800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-16300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-19300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,62 +1545,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-691800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-373800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-370400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-469100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>92200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-147600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1588,22 +1628,22 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1615,14 +1655,14 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1632,8 +1672,8 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1647,64 +1687,67 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-745400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-427200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-423900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-523200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-75100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-168000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15600</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1715,67 +1758,70 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-66300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-120400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-113700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-8500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-26700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,64 +1900,67 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-740000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-360900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-303500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-409600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>67700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-64300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-169400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23800</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1919,64 +1971,67 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-667600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-325400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-273500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-368700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>56200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-59200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-142300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23800</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,62 +2326,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E32" s="3">
         <v>40300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>14800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-64300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>20500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>140400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>16300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>19300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,64 +2397,67 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-667600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-325400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-273500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-368700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>56200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-59200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-142300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23800</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,64 +2539,67 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-667600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-325400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-273500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-368700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>56200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-59200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-142300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23800</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,50 +2742,51 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E41" s="3">
         <v>134500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>119500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>85700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>98100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>56500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>473100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>220700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2811,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2792,50 +2882,53 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E43" s="3">
         <v>166300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>132000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>132100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>179400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>154100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>160100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>155300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>104600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2851,8 +2944,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2860,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2928,50 +3024,53 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E45" s="3">
         <v>38600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,12 +3080,12 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3">
         <v>1300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,50 +3095,53 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>320400</v>
+      </c>
+      <c r="E46" s="3">
         <v>339400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>287800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>287600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>287700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>304400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>274700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>300800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>303600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>356100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>205100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>570300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>305300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3049,12 +3151,12 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
         <v>1300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3087,8 +3192,8 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>200</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>200</v>
@@ -3105,8 +3210,8 @@
       <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>200</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -3132,50 +3237,53 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E48" s="3">
         <v>88500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>91600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>88200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>91800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>94100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>101800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>101700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>82300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,8 +3299,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3200,50 +3308,53 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2641800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2684500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2732600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3493000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3525600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3978900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4402000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4428800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5040500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4938300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4986600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3423000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3440800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3259,8 +3370,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,50 +3521,53 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E52" s="3">
         <v>29200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3583,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,50 +3663,53 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3077100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3141700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3140500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3895900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3931100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4400200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4792400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4852200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5466000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5405500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5289200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4070800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3823100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,12 +3719,12 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
         <v>1300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,50 +3790,51 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E57" s="3">
         <v>32200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>58300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,12 +3844,12 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,50 +3859,53 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E58" s="3">
         <v>12700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>91400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,8 +3921,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3796,50 +3930,53 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>269200</v>
+      </c>
+      <c r="E59" s="3">
         <v>294000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>255800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>263700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>261200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>287000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>281100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>334000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>357800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>313600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>189700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>408900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>121800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3849,12 +3986,12 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,50 +4001,53 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>313500</v>
+      </c>
+      <c r="E60" s="3">
         <v>339000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>300400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>306600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>305800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>336200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>339800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>388800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>406500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>440400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>295600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>473600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>181400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,12 +4057,12 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,50 +4072,53 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1040200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1041200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1042100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1041300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1043000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1044700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1042500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1046500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1050000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>865500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>869600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>504800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>509000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4000,50 +4143,53 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E62" s="3">
         <v>176300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>172200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>188300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>205600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>292400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>392400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>422200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>566700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>615400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>717100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>657600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>821200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4053,12 +4199,12 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,50 +4427,53 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1620800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1656900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1625200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1719900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1741800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1896300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2028400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2111100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2320200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2219700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2182500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1955700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1877400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4325,12 +4483,12 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
         <v>1300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,50 +4809,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1912600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1873700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1831500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-803700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-530200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-535000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-166300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-155000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-211200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-152000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-131500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4691,11 +4865,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,50 +5093,53 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1456300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1484700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1515300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2176000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2189300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2503900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2764000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2741200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3145800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3185800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3106700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2115100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1945700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4963,11 +5149,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,64 +5311,67 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-667600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-325400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-273500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-368700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>56200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-59200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-142300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23800</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,67 +5411,68 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E83" s="3">
         <v>54000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>53800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>54100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>53300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,64 +5835,67 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E89" s="3">
         <v>28200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>36500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>39300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29800</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,67 +5935,68 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-3900</v>
       </c>
       <c r="S91" s="3">
         <v>-3900</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>-3900</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,67 +6146,70 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-146400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-781500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-469200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-3900</v>
       </c>
       <c r="S94" s="3">
         <v>-3900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>-3900</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,62 +6528,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>102300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>77700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>379700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>254000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>634100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>12300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,67 +6599,70 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6421,64 +6670,67 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E102" s="3">
         <v>19100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>103000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-412200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>251100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>149100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25500</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E7" s="2">
         <v>45443</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44804</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44712</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44620</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44074</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43982</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,70 +761,73 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E8" s="3">
         <v>151200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>158400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>157500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>158500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>166300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>164900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>160400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>144200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>137000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>78100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>84100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>83100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -831,65 +835,68 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>78500</v>
+        <v>52500</v>
       </c>
       <c r="E9" s="3">
-        <v>77900</v>
+        <v>53600</v>
       </c>
       <c r="F9" s="3">
-        <v>78900</v>
+        <v>52900</v>
       </c>
       <c r="G9" s="3">
-        <v>79300</v>
+        <v>53200</v>
       </c>
       <c r="H9" s="3">
-        <v>80700</v>
+        <v>54200</v>
       </c>
       <c r="I9" s="3">
-        <v>79300</v>
+        <v>54300</v>
       </c>
       <c r="J9" s="3">
+        <v>54200</v>
+      </c>
+      <c r="K9" s="3">
         <v>80800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>83300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>78700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>72800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>38200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>38400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,65 +909,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>72700</v>
+        <v>99700</v>
       </c>
       <c r="E10" s="3">
-        <v>80500</v>
+        <v>97500</v>
       </c>
       <c r="F10" s="3">
-        <v>78600</v>
+        <v>105600</v>
       </c>
       <c r="G10" s="3">
-        <v>79200</v>
+        <v>104300</v>
       </c>
       <c r="H10" s="3">
-        <v>79400</v>
+        <v>104300</v>
       </c>
       <c r="I10" s="3">
-        <v>87100</v>
+        <v>105800</v>
       </c>
       <c r="J10" s="3">
+        <v>112000</v>
+      </c>
+      <c r="K10" s="3">
         <v>84200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>77400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>81700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>71700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>64200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>52200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>51600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,65 +1013,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E12" s="3">
         <v>24800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>24900</v>
       </c>
       <c r="G12" s="3">
         <v>24900</v>
       </c>
       <c r="H12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="I12" s="3">
         <v>25900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>24900</v>
       </c>
       <c r="J12" s="3">
         <v>24900</v>
       </c>
       <c r="K12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="L12" s="3">
         <v>25600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,70 +1159,73 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
-        <v>1700</v>
+        <v>2800</v>
       </c>
       <c r="F14" s="3">
-        <v>717700</v>
+        <v>5900</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>713800</v>
       </c>
       <c r="H14" s="3">
-        <v>410400</v>
+        <v>-600</v>
       </c>
       <c r="I14" s="3">
-        <v>388700</v>
+        <v>407500</v>
       </c>
       <c r="J14" s="3">
+        <v>390800</v>
+      </c>
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>520400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>33200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1213,70 +1233,73 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20100</v>
+        <v>44800</v>
       </c>
       <c r="E15" s="3">
-        <v>20100</v>
+        <v>44700</v>
       </c>
       <c r="F15" s="3">
+        <v>44800</v>
+      </c>
+      <c r="G15" s="3">
+        <v>44600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="I15" s="3">
+        <v>44800</v>
+      </c>
+      <c r="J15" s="3">
+        <v>45000</v>
+      </c>
+      <c r="K15" s="3">
         <v>20000</v>
       </c>
-      <c r="G15" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>20100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>20300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>20000</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21500</v>
-      </c>
-      <c r="M15" s="3">
-        <v>19500</v>
       </c>
       <c r="N15" s="3">
         <v>19500</v>
       </c>
       <c r="O15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="P15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8500</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,67 +1334,68 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>168000</v>
+        <v>164700</v>
       </c>
       <c r="E17" s="3">
-        <v>172100</v>
+        <v>167500</v>
       </c>
       <c r="F17" s="3">
-        <v>888900</v>
+        <v>170000</v>
       </c>
       <c r="G17" s="3">
-        <v>184400</v>
+        <v>170000</v>
       </c>
       <c r="H17" s="3">
-        <v>582800</v>
+        <v>183700</v>
       </c>
       <c r="I17" s="3">
-        <v>555100</v>
+        <v>166300</v>
       </c>
       <c r="J17" s="3">
+        <v>166000</v>
+      </c>
+      <c r="K17" s="3">
         <v>171100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>696400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>174000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>191400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>91100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>121900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>83900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79300</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1379,65 +1406,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-16800</v>
+        <v>-12500</v>
       </c>
       <c r="E18" s="3">
-        <v>-13700</v>
+        <v>-16400</v>
       </c>
       <c r="F18" s="3">
-        <v>-731400</v>
+        <v>-11600</v>
       </c>
       <c r="G18" s="3">
-        <v>-25900</v>
+        <v>-12500</v>
       </c>
       <c r="H18" s="3">
-        <v>-422700</v>
+        <v>-25300</v>
       </c>
       <c r="I18" s="3">
-        <v>-388800</v>
+        <v>-6200</v>
       </c>
       <c r="J18" s="3">
+        <v>300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-535700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,65 +1510,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-27800</v>
+        <v>-7300</v>
       </c>
       <c r="E20" s="3">
-        <v>-40300</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>-14000</v>
+        <v>10000</v>
       </c>
       <c r="G20" s="3">
-        <v>-14800</v>
+        <v>-5500</v>
       </c>
       <c r="H20" s="3">
-        <v>-4400</v>
+        <v>-9400</v>
       </c>
       <c r="I20" s="3">
-        <v>-35000</v>
+        <v>-12200</v>
       </c>
       <c r="J20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K20" s="3">
         <v>3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>64300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-140400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>42800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-17600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-16300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,65 +1582,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9000</v>
+        <v>39700</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="F21" s="3">
-        <v>-691800</v>
+        <v>23200</v>
       </c>
       <c r="G21" s="3">
-        <v>13200</v>
+        <v>37600</v>
       </c>
       <c r="H21" s="3">
-        <v>-373800</v>
+        <v>28800</v>
       </c>
       <c r="I21" s="3">
-        <v>-370400</v>
+        <v>50800</v>
       </c>
       <c r="J21" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K21" s="3">
         <v>50100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-469100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>92200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-147600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,34 +1656,37 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>25200</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>25400</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>26600</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>25500</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>25700</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>22100</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1658,14 +1698,14 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1675,8 +1715,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1690,67 +1730,70 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-44700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-54100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-745400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-427200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-423900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-523200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-75100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15600</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1761,70 +1804,73 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-66300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-120400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-113700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-26700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-10800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-31400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,67 +1952,70 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-740000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-360900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-303500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-409600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>67700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-169400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-27100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23800</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -1974,67 +2026,70 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-667600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-325400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-273500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-368700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>56200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-59200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-27100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23800</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,65 +2396,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>27800</v>
+        <v>7300</v>
       </c>
       <c r="E32" s="3">
-        <v>40300</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>14000</v>
+        <v>-10000</v>
       </c>
       <c r="G32" s="3">
-        <v>14800</v>
+        <v>5500</v>
       </c>
       <c r="H32" s="3">
-        <v>4400</v>
+        <v>9400</v>
       </c>
       <c r="I32" s="3">
-        <v>35000</v>
+        <v>12200</v>
       </c>
       <c r="J32" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-64300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>140400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-42800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>17600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>16300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,67 +2470,70 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-667600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-325400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-273500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-368700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>56200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-59200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-27100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23800</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,67 +2618,70 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-667600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-325400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-273500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-368700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>56200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-59200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-27100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23800</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2613,73 +2692,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E38" s="2">
         <v>45443</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44804</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44712</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44620</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44074</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43982</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2771,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,53 +2829,54 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E41" s="3">
         <v>160200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>134500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>119500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>93000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>85700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>98100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>56500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>473100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>220700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2826,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -2885,53 +2975,56 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E43" s="3">
         <v>119400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>166300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>132000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>132100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>179400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>154100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>160100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>123300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>155300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>104600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>60600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2947,8 +3040,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -2956,31 +3049,34 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3027,53 +3123,56 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>40800</v>
+        <v>9800</v>
       </c>
       <c r="E45" s="3">
-        <v>38600</v>
+        <v>9700</v>
       </c>
       <c r="F45" s="3">
-        <v>45500</v>
+        <v>9200</v>
       </c>
       <c r="G45" s="3">
-        <v>48300</v>
+        <v>7600</v>
       </c>
       <c r="H45" s="3">
-        <v>36100</v>
+        <v>8000</v>
       </c>
       <c r="I45" s="3">
-        <v>31900</v>
+        <v>7600</v>
       </c>
       <c r="J45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K45" s="3">
         <v>35000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23900</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,12 +3182,12 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,53 +3197,56 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>307300</v>
+      </c>
+      <c r="E46" s="3">
         <v>320400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>339400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>287800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>287600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>287700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>304400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>274700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>300800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>303600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>356100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>205100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>570300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>305300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,12 +3256,12 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
         <v>1300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3180,11 +3285,11 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1000</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -3195,8 +3300,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>200</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>200</v>
@@ -3213,8 +3318,8 @@
       <c r="P47" s="3">
         <v>200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>200</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3240,53 +3345,56 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E48" s="3">
         <v>85300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>88200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>91200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>101800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>82300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>67000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>68100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,8 +3410,8 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3311,53 +3419,56 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2611400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2641800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2684500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2732600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3493000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3525600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3978900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4402000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4428800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5040500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4938300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4986600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3423000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3440800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3373,8 +3484,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,53 +3641,56 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>29700</v>
+        <v>14300</v>
       </c>
       <c r="E52" s="3">
-        <v>29200</v>
+        <v>15100</v>
       </c>
       <c r="F52" s="3">
-        <v>28600</v>
+        <v>14300</v>
       </c>
       <c r="G52" s="3">
-        <v>27100</v>
+        <v>14400</v>
       </c>
       <c r="H52" s="3">
-        <v>26100</v>
+        <v>16300</v>
       </c>
       <c r="I52" s="3">
-        <v>25700</v>
+        <v>9900</v>
       </c>
       <c r="J52" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K52" s="3">
         <v>21500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,8 +3706,8 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,53 +3789,56 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3031500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3077100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3141700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3140500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3895900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3931100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4400200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4792400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4852200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5466000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5405500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5289200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4070800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3823100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,12 +3848,12 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
         <v>1300</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,53 +3921,54 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>31600</v>
+        <v>29200</v>
       </c>
       <c r="E57" s="3">
-        <v>32200</v>
+        <v>29000</v>
       </c>
       <c r="F57" s="3">
-        <v>32300</v>
+        <v>29700</v>
       </c>
       <c r="G57" s="3">
-        <v>31200</v>
+        <v>29700</v>
       </c>
       <c r="H57" s="3">
-        <v>31000</v>
+        <v>28600</v>
       </c>
       <c r="I57" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>32900</v>
+      </c>
+      <c r="K57" s="3">
+        <v>35800</v>
+      </c>
+      <c r="L57" s="3">
+        <v>41700</v>
+      </c>
+      <c r="M57" s="3">
+        <v>35600</v>
+      </c>
+      <c r="N57" s="3">
         <v>35400</v>
       </c>
-      <c r="J57" s="3">
-        <v>35800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>41700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>35600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>35400</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>94500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>58300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,12 +3978,12 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,53 +3993,56 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12800</v>
+        <v>20200</v>
       </c>
       <c r="E58" s="3">
-        <v>12700</v>
+        <v>19700</v>
       </c>
       <c r="F58" s="3">
-        <v>12200</v>
+        <v>20100</v>
       </c>
       <c r="G58" s="3">
-        <v>11700</v>
+        <v>19600</v>
       </c>
       <c r="H58" s="3">
-        <v>13600</v>
+        <v>19100</v>
       </c>
       <c r="I58" s="3">
-        <v>13700</v>
+        <v>21400</v>
       </c>
       <c r="J58" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K58" s="3">
         <v>23000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>91400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3924,8 +4058,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -3933,53 +4067,56 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>269200</v>
+        <v>216500</v>
       </c>
       <c r="E59" s="3">
-        <v>294000</v>
+        <v>223100</v>
       </c>
       <c r="F59" s="3">
-        <v>255800</v>
+        <v>247000</v>
       </c>
       <c r="G59" s="3">
-        <v>263700</v>
+        <v>214600</v>
       </c>
       <c r="H59" s="3">
-        <v>261200</v>
+        <v>228200</v>
       </c>
       <c r="I59" s="3">
-        <v>287000</v>
+        <v>211900</v>
       </c>
       <c r="J59" s="3">
+        <v>232000</v>
+      </c>
+      <c r="K59" s="3">
         <v>281100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>334000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>357800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>313600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>189700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>408900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3989,12 +4126,12 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,53 +4141,56 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>298800</v>
+      </c>
+      <c r="E60" s="3">
         <v>313500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>339000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>306600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>305800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>336200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>339800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>388800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>406500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>440400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>295600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>473600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>181400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4060,12 +4200,12 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,53 +4215,56 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1040200</v>
+        <v>1052200</v>
       </c>
       <c r="E61" s="3">
-        <v>1041200</v>
+        <v>1055100</v>
       </c>
       <c r="F61" s="3">
-        <v>1042100</v>
+        <v>1058600</v>
       </c>
       <c r="G61" s="3">
-        <v>1041300</v>
+        <v>1060100</v>
       </c>
       <c r="H61" s="3">
-        <v>1043000</v>
+        <v>1056500</v>
       </c>
       <c r="I61" s="3">
-        <v>1044700</v>
+        <v>1060100</v>
       </c>
       <c r="J61" s="3">
+        <v>1060100</v>
+      </c>
+      <c r="K61" s="3">
         <v>1042500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1046500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1050000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>865500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>869600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>504800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>509000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4146,53 +4289,56 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>171900</v>
+        <v>90300</v>
       </c>
       <c r="E62" s="3">
-        <v>176300</v>
+        <v>105600</v>
       </c>
       <c r="F62" s="3">
-        <v>172200</v>
+        <v>101300</v>
       </c>
       <c r="G62" s="3">
-        <v>188300</v>
+        <v>85400</v>
       </c>
       <c r="H62" s="3">
-        <v>205600</v>
+        <v>97800</v>
       </c>
       <c r="I62" s="3">
-        <v>292400</v>
+        <v>108700</v>
       </c>
       <c r="J62" s="3">
+        <v>130000</v>
+      </c>
+      <c r="K62" s="3">
         <v>392400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>422200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>566700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>615400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>717100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>657600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>821200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,12 +4348,12 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,53 +4585,56 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1620800</v>
+        <v>1491700</v>
       </c>
       <c r="E66" s="3">
-        <v>1656900</v>
+        <v>1525600</v>
       </c>
       <c r="F66" s="3">
-        <v>1625200</v>
+        <v>1556500</v>
       </c>
       <c r="G66" s="3">
-        <v>1719900</v>
+        <v>1514700</v>
       </c>
       <c r="H66" s="3">
-        <v>1741800</v>
+        <v>1536100</v>
       </c>
       <c r="I66" s="3">
-        <v>1896300</v>
+        <v>1554300</v>
       </c>
       <c r="J66" s="3">
+        <v>1673300</v>
+      </c>
+      <c r="K66" s="3">
         <v>2028400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2111100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2320200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2219700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2182500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1955700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1877400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4486,12 +4644,12 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,53 +4983,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1942400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1912600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1873700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1831500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-803700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-530200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-535000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-166300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-155000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-211200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-131500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4868,11 +5042,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,53 +5279,56 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1448500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1456300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1484700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1515300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2176000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2189300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2503900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2764000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2741200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3145800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3185800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3106700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2115100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1945700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5152,11 +5338,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5427,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E80" s="2">
         <v>45443</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44804</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44712</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44620</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44074</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43982</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,67 +5506,70 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-667600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-325400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-273500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-368700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>56200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-59200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-27100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23800</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,70 +5610,71 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>53600</v>
+        <v>8900</v>
       </c>
       <c r="E83" s="3">
-        <v>54000</v>
+        <v>8600</v>
       </c>
       <c r="F83" s="3">
-        <v>53600</v>
+        <v>8400</v>
       </c>
       <c r="G83" s="3">
-        <v>53800</v>
+        <v>8600</v>
       </c>
       <c r="H83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>52500</v>
+      </c>
+      <c r="L83" s="3">
+        <v>54100</v>
+      </c>
+      <c r="M83" s="3">
         <v>53300</v>
       </c>
-      <c r="I83" s="3">
-        <v>53400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>52500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>54100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>53300</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>50500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,67 +6052,70 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E89" s="3">
         <v>35900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>39300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29800</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,70 +6156,71 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-3900</v>
       </c>
       <c r="T91" s="3">
         <v>-3900</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>-3900</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,70 +6376,73 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-146400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-781500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-469200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-3900</v>
       </c>
       <c r="T94" s="3">
         <v>-3900</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>-3900</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,31 +6480,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6774,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>102300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>77700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>379700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>254000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>634100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>12300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,70 +6848,73 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L101" s="3">
+        <v>800</v>
+      </c>
+      <c r="M101" s="3">
+        <v>900</v>
+      </c>
+      <c r="N101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>500</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G101" s="3">
-        <v>800</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>900</v>
-      </c>
-      <c r="M101" s="3">
-        <v>12000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T101" s="3">
-        <v>100</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -6673,67 +6922,70 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E102" s="3">
         <v>26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>103000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-412200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>251100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>149100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E7" s="2">
         <v>45535</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45351</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45077</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44804</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44712</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44620</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44074</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43982</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -764,73 +764,76 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E8" s="3">
         <v>152200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>157500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>160100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>164900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>160700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>160400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>144200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>137000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>78100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>66300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>81800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>83100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -838,68 +841,71 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E9" s="3">
         <v>52500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>53600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>52900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>80800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>83300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>78700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>72500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>72800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>38200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>38400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,68 +918,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E10" s="3">
         <v>99700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>105600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>104300</v>
       </c>
       <c r="H10" s="3">
         <v>104300</v>
       </c>
       <c r="I10" s="3">
+        <v>104300</v>
+      </c>
+      <c r="J10" s="3">
         <v>105800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>84200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>51600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>52300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,68 +1026,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E12" s="3">
         <v>26000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>24900</v>
       </c>
       <c r="H12" s="3">
         <v>24900</v>
       </c>
       <c r="I12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="J12" s="3">
         <v>25900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>24900</v>
       </c>
       <c r="K12" s="3">
         <v>24900</v>
       </c>
       <c r="L12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="M12" s="3">
         <v>25600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,73 +1178,76 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>370600</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>713800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>407500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>390800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>520400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>33200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1236,73 +1255,76 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E15" s="3">
         <v>44800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21500</v>
-      </c>
-      <c r="N15" s="3">
-        <v>19500</v>
       </c>
       <c r="O15" s="3">
         <v>19500</v>
       </c>
       <c r="P15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8500</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1310,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,70 +1360,71 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E17" s="3">
         <v>164700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>167500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>170000</v>
       </c>
       <c r="G17" s="3">
         <v>170000</v>
       </c>
       <c r="H17" s="3">
+        <v>170000</v>
+      </c>
+      <c r="I17" s="3">
         <v>183700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>166300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>166000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>171100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>696400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>174000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>167400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>191400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>91100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>121900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>83900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>76800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>79300</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1409,68 +1435,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-535700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-27400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,68 +1543,69 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>64300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-20500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-140400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>42800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-16300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,68 +1618,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E21" s="3">
         <v>39700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>37600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>28800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>50100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-469100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>92200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-147600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,37 +1695,40 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E22" s="3">
         <v>25200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1701,14 +1740,14 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1718,8 +1757,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1733,70 +1772,73 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-384100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-44700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-745400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-427200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-423900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-523200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-75100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-168000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15600</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1807,73 +1849,76 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-66300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-120400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-113700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-26700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-31400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8200</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1881,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,70 +2003,73 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-381600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-42800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-740000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-360900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-303500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-409600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>67700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-64300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-169400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-27100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23800</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2029,70 +2080,73 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-346900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-42200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-667600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-325400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-273500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-368700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>56200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-59200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-142300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-27100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23800</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2103,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,68 +2465,71 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E32" s="3">
         <v>7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-64300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>20500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>140400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-42800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>16300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,70 +2542,73 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-346900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-42200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-667600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-325400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-273500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-368700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>56200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-59200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-142300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-27100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23800</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2547,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,70 +2696,73 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-346900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-42200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-667600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-325400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-273500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-368700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>56200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-59200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-142300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-27100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23800</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2695,76 +2773,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E38" s="2">
         <v>45535</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45351</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45077</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44804</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44712</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44074</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43982</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,56 +2915,57 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E41" s="3">
         <v>142200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>160200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>134500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>119500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>155500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>56500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>473100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>220700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +2990,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2916,11 +3005,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>900</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2978,56 +3067,59 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E43" s="3">
         <v>120900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>119400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>166300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>132000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>132100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>179400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>154100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>160100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>123300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>155300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>104600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>60600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3135,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3052,8 +3144,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3078,8 +3173,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3126,56 +3221,59 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3185,12 +3283,12 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3">
         <v>1300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,56 +3298,59 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>333600</v>
+      </c>
+      <c r="E46" s="3">
         <v>307300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>320400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>339400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>287800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>287600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>287700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>304400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>274700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>300800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>303600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>356100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>205100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>570300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>305300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3259,12 +3360,12 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
         <v>1300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3285,14 +3389,14 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>1000</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>1000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -3303,8 +3407,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>200</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>200</v>
@@ -3321,8 +3425,8 @@
       <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>200</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3348,56 +3452,59 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E48" s="3">
         <v>82800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>85300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>88500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>91600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>88200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>91800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>91200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>82300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>67000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>68100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3413,8 +3520,8 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3422,56 +3529,59 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2179200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2611400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2641800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2684500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2732600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3493000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3525600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3978900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4402000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4428800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5040500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4938300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4986600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3423000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3440800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3487,8 +3597,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3496,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,56 +3760,59 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E52" s="3">
         <v>14300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,8 +3828,8 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3718,8 +3837,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,56 +3914,59 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2622100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3031500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3077100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3141700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3140500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3895900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3931100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4400200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4792400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4852200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5466000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5405500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5289200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4070800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3823100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3851,12 +3976,12 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
         <v>1300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,56 +4051,57 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E57" s="3">
         <v>29200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>29700</v>
       </c>
       <c r="G57" s="3">
         <v>29700</v>
       </c>
       <c r="H57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="I57" s="3">
         <v>28600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>58300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3981,12 +4111,12 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,56 +4126,59 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E58" s="3">
         <v>20200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>91400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,8 +4194,8 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4070,56 +4203,59 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E59" s="3">
         <v>216500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>223100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>247000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>214600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>228200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>211900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>281100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>334000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>357800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>313600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>189700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>408900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,12 +4265,12 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,56 +4280,59 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>309300</v>
+      </c>
+      <c r="E60" s="3">
         <v>298800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>313500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>339000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>300400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>306600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>305800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>336200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>339800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>388800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>406500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>440400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>295600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>473600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>181400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,12 +4342,12 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,56 +4357,59 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1048700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1052200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1055100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1058600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1060100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1056500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1060100</v>
       </c>
       <c r="J61" s="3">
         <v>1060100</v>
       </c>
       <c r="K61" s="3">
+        <v>1060100</v>
+      </c>
+      <c r="L61" s="3">
         <v>1042500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1046500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1050000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>865500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>869600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>504800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>509000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4292,56 +4434,59 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E62" s="3">
         <v>90300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>105600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>101300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>85400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>97800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>130000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>392400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>422200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>566700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>615400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>717100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>657600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>821200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,12 +4496,12 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
         <v>800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,56 +4742,59 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1491700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1525600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1556500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1514700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1536100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1554300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1673300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2028400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2111100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2320200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2219700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2182500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1955700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1877400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,12 +4804,12 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
         <v>1300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,56 +5156,59 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2289300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1942400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1912600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1873700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1831500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-803700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-530200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-535000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-166300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-155000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-211200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-131500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5045,11 +5218,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5060,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,56 +5464,59 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1087600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1448500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1456300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1484700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1515300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2176000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2189300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2503900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2764000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2741200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3145800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3185800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3106700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2115100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1945700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5341,11 +5526,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5356,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,76 +5618,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E80" s="2">
         <v>45535</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45351</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45077</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44804</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44712</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44620</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44074</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43982</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5509,70 +5700,73 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-346900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-42200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-667600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-325400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-273500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-368700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>56200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-59200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-142300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-27100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23800</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5583,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,73 +5808,74 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>52500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>54100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>50500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5685,8 +5883,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,70 +6268,73 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>35900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>36500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>41000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>39300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29800</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6129,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,8 +6376,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6166,64 +6386,64 @@
         <v>-6200</v>
       </c>
       <c r="E91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-3900</v>
       </c>
       <c r="U91" s="3">
         <v>-3900</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>-3900</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6231,8 +6451,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,8 +6605,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6388,64 +6617,64 @@
         <v>-6200</v>
       </c>
       <c r="E94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-146400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-781500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-469200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-3900</v>
       </c>
       <c r="U94" s="3">
         <v>-3900</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>-3900</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6453,8 +6682,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6507,8 +6740,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6555,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,8 +7019,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6786,59 +7031,59 @@
         <v>-3300</v>
       </c>
       <c r="E100" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>102300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>77700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>379700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>254000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>634100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>12300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6851,73 +7096,76 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -6925,70 +7173,73 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>103000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-412200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>251100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>149100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25500</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -6997,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ETWO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>ETWO</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E7" s="2">
         <v>45626</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45535</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45443</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45351</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45260</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45169</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45077</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44985</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44895</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44804</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44712</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44530</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44439</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44347</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44255</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44165</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44074</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43982</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,76 +768,79 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E8" s="3">
         <v>151700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>152200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>158400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>157500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>158500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>160100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>164900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>160700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>160400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>144200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>137000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>78100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>66300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>84100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>81800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>83100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -844,71 +848,74 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E9" s="3">
         <v>52100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>52500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>53600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>52900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>80800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>83300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>78700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>72500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>72800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>38200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>38400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>31900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>30800</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,71 +928,74 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E10" s="3">
         <v>99500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>99700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>105600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>104300</v>
       </c>
       <c r="I10" s="3">
         <v>104300</v>
       </c>
       <c r="J10" s="3">
+        <v>104300</v>
+      </c>
+      <c r="K10" s="3">
         <v>105800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>84200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>64200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>51600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>52300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1040,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E12" s="3">
         <v>23300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>24900</v>
       </c>
       <c r="I12" s="3">
         <v>24900</v>
       </c>
       <c r="J12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K12" s="3">
         <v>25900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>24900</v>
       </c>
       <c r="L12" s="3">
         <v>24900</v>
       </c>
       <c r="M12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="N12" s="3">
         <v>25600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14600</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,76 +1198,79 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E14" s="3">
         <v>370600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>713800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>407500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>390800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>520400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>33200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1258,76 +1278,79 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E15" s="3">
         <v>29300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>19500</v>
       </c>
       <c r="P15" s="3">
         <v>19500</v>
       </c>
       <c r="Q15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="R15" s="3">
         <v>3500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8500</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,73 +1387,74 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E17" s="3">
         <v>147100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>164700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>167500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>170000</v>
       </c>
       <c r="H17" s="3">
         <v>170000</v>
       </c>
       <c r="I17" s="3">
+        <v>170000</v>
+      </c>
+      <c r="J17" s="3">
         <v>183700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>166300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>166000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>171100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>696400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>174000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>167400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>191400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>91100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>93700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>121900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>83900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>76800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>79300</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1438,71 +1465,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-535700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-27400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,71 +1577,72 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>64300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-140400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>42800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-17600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-16300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,71 +1655,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E21" s="3">
         <v>41300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>37600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>50800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>50100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-469100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>92200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-147600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,40 +1735,43 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E22" s="3">
         <v>25400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1743,14 +1783,14 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1800,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1775,73 +1815,76 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-264900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-384100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-44700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-54100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-745400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-427200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-423900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-523200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-75100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-168000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15600</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1852,76 +1895,79 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-8500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-66300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-120400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-113700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-26700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-31400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,73 +2055,76 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-268500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-381600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-740000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-360900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-303500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-409600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>67700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-169400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-27100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23800</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2083,73 +2135,76 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-244200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-346900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-42200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-667600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-325400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-273500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-368700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>56200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-142300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-27100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-23800</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,71 +2535,74 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>7400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-64300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>20500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>140400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-42800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>17600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>16300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,73 +2615,76 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-244200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-346900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-42200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-667600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-325400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-273500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-368700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>56200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-142300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23800</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,73 +2775,76 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-244200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-346900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-42200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-667600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-325400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-273500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-368700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>56200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-142300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23800</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2776,79 +2855,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E38" s="2">
         <v>45626</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45535</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45443</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45351</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45260</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45169</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45077</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44985</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44895</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44804</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44712</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44530</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44439</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44347</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44255</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44165</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44074</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43982</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,59 +3002,60 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>197400</v>
+      </c>
+      <c r="E41" s="3">
         <v>151200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>142200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>160200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>134500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>119500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>85700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>129200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>56500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>473100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>220700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,8 +3080,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3008,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3070,59 +3160,62 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138600</v>
+      </c>
+      <c r="E43" s="3">
         <v>139700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>119400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>166300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>132000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>132100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>179400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>154100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>160100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>123300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>155300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>104600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>67600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3138,8 +3231,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,8 +3272,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3224,59 +3320,62 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E45" s="3">
         <v>10500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9700</v>
       </c>
-      <c r="G45" s="3">
-        <v>9200</v>
-      </c>
       <c r="H45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>45300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23900</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3286,12 +3385,12 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,59 +3400,62 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E46" s="3">
         <v>333600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>307300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>320400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>339400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>287800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>287600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>287700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>304400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>274700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>300800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>303600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>356100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>205100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>570300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>305300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,12 +3465,12 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3">
         <v>1300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,13 +3480,16 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -3392,15 +3497,15 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
+        <v>200</v>
+      </c>
+      <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3410,8 +3515,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>200</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>200</v>
@@ -3428,8 +3533,8 @@
       <c r="R47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3455,59 +3560,62 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E48" s="3">
         <v>79700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>82800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>85300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>88500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>91800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>91200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>82300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>67000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>68100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,8 +3631,8 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3532,59 +3640,62 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1886800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2179200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2611400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2641800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2684500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2732600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3493000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3525600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3978900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4402000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4428800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5040500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4938300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4986600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3423000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3440800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3600,8 +3711,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,59 +3880,62 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>13700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15100</v>
       </c>
-      <c r="G52" s="3">
-        <v>14300</v>
-      </c>
       <c r="H52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I52" s="3">
         <v>14400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3831,8 +3951,8 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,59 +4040,62 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2371000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2622100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3031500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3077100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3141700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3140500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3895900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3931100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4400200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4792400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4852200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5466000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5405500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5289200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4070800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3823100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3979,12 +4105,12 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3">
         <v>1300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,59 +4182,60 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E57" s="3">
         <v>27100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>29700</v>
       </c>
       <c r="H57" s="3">
         <v>29700</v>
       </c>
       <c r="I57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="J57" s="3">
         <v>28600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>94500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>58300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>51600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,12 +4245,12 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,59 +4260,62 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E58" s="3">
         <v>20100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>91400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,8 +4331,8 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4206,59 +4340,62 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>248700</v>
+      </c>
+      <c r="E59" s="3">
         <v>229900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>216500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>223100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>247000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>214600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>211900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>281100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>334000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>357800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>313600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>189700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>408900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>121800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4268,12 +4405,12 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,59 +4420,62 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>333400</v>
+      </c>
+      <c r="E60" s="3">
         <v>309300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>298800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>313500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>339000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>306600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>305800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>336200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>339800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>388800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>406500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>440400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>295600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>473600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>181400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4345,12 +4485,12 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,59 +4500,62 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1045200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1048700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1052200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1055100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1058600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1060100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1056500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1060100</v>
       </c>
       <c r="K61" s="3">
         <v>1060100</v>
       </c>
       <c r="L61" s="3">
+        <v>1060100</v>
+      </c>
+      <c r="M61" s="3">
         <v>1042500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1046500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1050000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>865500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>869600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>504800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>509000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4437,59 +4580,62 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E62" s="3">
         <v>75400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>90300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>105600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>101300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>85400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>108700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>130000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>392400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>422200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>566700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>615400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>717100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>657600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>821200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4499,12 +4645,12 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,59 +4900,62 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1494100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1478000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1491700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1525600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1556500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1514700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1536100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1554300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1673300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2028400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2111100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2320200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2219700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2182500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1955700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1877400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4807,12 +4965,12 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3">
         <v>1300</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,59 +5330,62 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2533500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2289300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1942400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1912600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1873700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1831500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1163900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1129100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-803700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-530200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-535000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-166300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-155000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-211200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-152000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-131500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5221,11 +5395,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,59 +5650,62 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>844800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1087600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1448500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1456300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1484700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1515300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2176000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2189300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2503900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2764000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2741200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3145800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3185800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3106700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2115100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1945700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5529,11 +5715,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,79 +5810,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E80" s="2">
         <v>45626</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45535</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45443</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45351</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45260</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45169</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45077</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44985</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44895</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44804</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44712</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44530</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44439</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44347</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44255</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44165</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44074</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43982</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,73 +5895,76 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-244200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-346900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-42200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-667600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-325400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-273500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-368700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>56200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-142300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23800</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,76 +6007,77 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>52500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>54100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>53300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>51100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>50500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>16900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,73 +6485,76 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E89" s="3">
         <v>17700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>35900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>36500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>39300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29800</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,76 +6597,77 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6200</v>
+        <v>-6700</v>
       </c>
       <c r="E91" s="3">
         <v>-6200</v>
       </c>
       <c r="F91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-3900</v>
       </c>
       <c r="V91" s="3">
         <v>-3900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>-3900</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,76 +6835,79 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6200</v>
+        <v>-6700</v>
       </c>
       <c r="E94" s="3">
         <v>-6200</v>
       </c>
       <c r="F94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-6100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-146400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-781500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-469200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-3900</v>
       </c>
       <c r="V94" s="3">
         <v>-3900</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>-3900</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6977,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,8 +7265,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7034,59 +7280,59 @@
         <v>-3300</v>
       </c>
       <c r="F100" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>102300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>77700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>379700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>254000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>634100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>12300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-19700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,76 +7345,79 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>12000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7176,73 +7425,76 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E102" s="3">
         <v>9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>103000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-412200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>251100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>149100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>25500</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
